--- a/public/downloads/NhanSinter-resistant2025.xlsx
+++ b/public/downloads/NhanSinter-resistant2025.xlsx
@@ -17404,13 +17404,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.4841353151971622</v>
+        <v>0.4832086063369182</v>
       </c>
       <c r="I3" s="4">
-        <v>0.4233445852709029</v>
+        <v>0.4219884259632286</v>
       </c>
       <c r="J3" s="4">
-        <v>0.3423777633639897</v>
+        <v>0.337797869001142</v>
       </c>
       <c r="K3" s="4">
         <v>85.17517006802743</v>
@@ -17454,13 +17454,13 @@
         <v>3.333333333333333</v>
       </c>
       <c r="H4" s="4">
-        <v>0.5508115404782468</v>
+        <v>0.5227492558940471</v>
       </c>
       <c r="I4" s="4">
-        <v>0.3874711475054631</v>
+        <v>0.3064088768725612</v>
       </c>
       <c r="J4" s="4">
-        <v>0.4827299151025932</v>
+        <v>0.4627639439949559</v>
       </c>
       <c r="K4" s="4">
         <v>72.43990929705191</v>
@@ -17504,13 +17504,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.361807784165173</v>
+        <v>0.3560602252031659</v>
       </c>
       <c r="I5" s="4">
-        <v>0.3127096340496345</v>
+        <v>0.3055251853471257</v>
       </c>
       <c r="J5" s="4">
-        <v>0.2940831642290299</v>
+        <v>0.2947526242037055</v>
       </c>
       <c r="K5" s="4">
         <v>82.47335600907034</v>
@@ -17554,13 +17554,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.3125142960420982</v>
+        <v>0.311712415992185</v>
       </c>
       <c r="I6" s="4">
-        <v>0.2907313089299142</v>
+        <v>0.289430962903028</v>
       </c>
       <c r="J6" s="4">
-        <v>0.3565241411451234</v>
+        <v>0.3542373917384393</v>
       </c>
       <c r="K6" s="4">
         <v>83.6887755102035</v>
@@ -17654,10 +17654,10 @@
         <v>1.666666666666667</v>
       </c>
       <c r="H8" s="4">
-        <v>0.5493978835014838</v>
+        <v>0.5421423346203249</v>
       </c>
       <c r="I8" s="4">
-        <v>0.39757162380372</v>
+        <v>0.3858058688613004</v>
       </c>
       <c r="J8" s="4">
         <v>0.3618661363962284</v>
@@ -17704,13 +17704,13 @@
         <v>1.666666666666667</v>
       </c>
       <c r="H9" s="4">
-        <v>0.6545370807886772</v>
+        <v>0.6544817117283483</v>
       </c>
       <c r="I9" s="4">
-        <v>0.5996293533589937</v>
+        <v>0.5918235183845368</v>
       </c>
       <c r="J9" s="4">
-        <v>0.7324563127540098</v>
+        <v>0.725801993896805</v>
       </c>
       <c r="K9" s="4">
         <v>75.39229024943309</v>
@@ -17754,13 +17754,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.2714331960704893</v>
+        <v>0.2684781525163749</v>
       </c>
       <c r="I10" s="4">
-        <v>0.2789635997106989</v>
+        <v>0.2756802179839051</v>
       </c>
       <c r="J10" s="4">
-        <v>0.2859230774649995</v>
+        <v>0.2825604388030269</v>
       </c>
       <c r="K10" s="4">
         <v>85.36394557823124</v>
@@ -17804,13 +17804,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.8232532433126996</v>
+        <v>0.8215652904203374</v>
       </c>
       <c r="I11" s="4">
-        <v>0.4118538469304361</v>
+        <v>0.4062273372892291</v>
       </c>
       <c r="J11" s="4">
-        <v>0.2890148094626799</v>
+        <v>0.286026387160162</v>
       </c>
       <c r="K11" s="4">
         <v>70.99319727891196</v>
@@ -17854,13 +17854,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.2716072097337029</v>
+        <v>0.2689001227497629</v>
       </c>
       <c r="I12" s="4">
-        <v>0.2531135405876667</v>
+        <v>0.2498650362069387</v>
       </c>
       <c r="J12" s="4">
-        <v>0.1954312497855441</v>
+        <v>0.1941656097417083</v>
       </c>
       <c r="K12" s="4">
         <v>77.82993197278942</v>
